--- a/vse-loti/339782140/spec-339782140.xlsx
+++ b/vse-loti/339782140/spec-339782140.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -60,13 +61,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -453,61 +457,3649 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Наименование позиции (⌀ + s, если указано)</t>
+          <t>Наименование позиции</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>D×s, мм</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Кол-во (исх.)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Масса, т (приведённая)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Бур SDS+16х460мм</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>16×460</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Бур SDS+16х800 мм</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>16×800</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Бур по бетону 6*160 мм</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Гайка М 8</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Гайка М6 ГОСТ 5927-70</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Гайка М 10 оцинкованная</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Дюбель 6х37 без бортика</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Дюбель ежик 6*60 тип К</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Изолента профессиональная черная</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>штука 12 Гайка оцинкованная М16</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" s="2" t="n">
+        <v>750</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Герметик силиконовый санитарный в тубах</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>вн.р. сталь</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>нар.р. сталь</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>вн.р. сталь</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>нар.р. сталь</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>вн.р. латун</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>нар.р. латун</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Заглушка 32 вн.р. латун</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Заглушка 32 нар.р. латун</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Заглушка 40 вн.р. сталь</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Заглушка 40 нар.р. сталь</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Заглушка канализационная ПП 110</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Заглушка пп.20</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Заглушка пп.25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Заглушка пп.32</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Заглушка пп.40</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Заглушка пп.63</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Задвижка 30(31)ч6бр Ду 80</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Задвижка 30(31)ч6бр ДУ50</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Контргайка 15 сталь</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Контргайка 20 сталь</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Контргайка 25 сталь</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Кран п/п 40</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Кран п/п 63</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Кран Маевского 1/2 под отвертку</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>40×1.1</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Кран шаровый Ci КЩЦФ Ду100 Ру16 ст.20</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD КЩЦФ Ду50/40 Ру40 ст. фланц.20</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Кран шаровый LD КЩЦФ Ду80/70 Ру16 ст. фланц</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Кран шаровый ДУ-15 г/г ручка ГАЛЛОП</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Кран шаровый ДУ-20 г/г ручка ГАЛЛОП</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Кран шаровый ДУ-20 г/ш ручка ГАЛЛОП (уп50)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Кран шаровый Ду-25 г/г ручка Галлоп</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Кран шаровый ДУ-25 г/ш ручка ГОЛЛОП ( уп.30)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Кран шаровый ДУ-32г/г ручка ГАЛЛОП</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Кран шаровый п/п 32</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>кран шаровый п/п d-20</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>кран шаровый п/п d-25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Креп хомут с шуруп/дюб 4" 107-115</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Крестовина 25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Крестовина 32</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Кронштейн для радиатора с дюбелем удлиненный</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>штука 57 Муфта комб. внутр. рез.d 32х1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>32×1</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Муфта комб. внутр. рез.d 32х1.1/4</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>32×1.1</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Муфта ДУ-15 сталь</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Муфта канализационная 110 ремонтн.переходн.чугун-пластик</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Муфта канализационная ПП 110</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Муфта комб.внутр. рез. d 32х3/4</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>32×3</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>штука 64 Муфта комб.внутр. рез. d20х1/2"(50/150)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>20×1</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Муфта комб.внутр. рез. d25х1/2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>25×1</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Муфта комб.внутр. рез. d25х3/4</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>25×3</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Муфта комб.внутр. рез. d40х1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>40×1</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Муфта комб.внутр. рез. d40х1.1/2</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>40×1.1</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Муфта комб.внутр. рез. d40х1.1/4"ТЕВО (5/35)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>40×1.1</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Муфта комб.наруж. рез. d20 х 1/2"</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>20×1</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Муфта комб.наруж. рез. d20х3/4"</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>20×3</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Муфта комб.наруж. рез. d25х 1"</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>25×1</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Муфта комб.наруж. рез. d25х1/2"ТЕВО (40/160)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>25×1</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Муфта комб.наруж. рез. d32х1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>32×1</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Муфта комб.наруж. рез. d32х1.1/4"</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>32×1.1</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Муфта комб.наруж. рез. d32х3/4"</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>32×3</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Муфта комб.наруж. рез. d40 х 1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>40×1</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Муфта комб.наруж. рез. d40 х 1.1/2"</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>40×1.1</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Муфта комб.наруж. рез. под ключ d40 х 1.1/4</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>40×1.1</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Муфта п/п d-25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Муфта п/п d-40</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Муфта рем 50</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Муфта соед. 63 ТЕВО</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Нипель переходной 3/4 н 1/2 н</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Отвод 110/45</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Отвод 110/87</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Отвод 50/45</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Отвод 50/87</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Отвод 57</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>штука 92 Переход на чугун d 110х123 трехлепестковый</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>110×123</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Переход ПП эксц. 100*50мм</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Переход стальной 89*57</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Пробка левая проходная Ду15 д/чугун. радиат</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Пробка правая проходная Ду15 д/чугун. радиат</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>проходная Ду 20 для чугунного радиатора</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Пробка правая проходная Ду 20 для чугунного радиатора</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Прокладка паронит Ду 100 для ФЛАНЦА</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Прокладка паронит Ду 40 для ФЛАНЦА</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Прокладка паронит Ду 50 для ФЛАНЦА</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Прокладка паронит Ду 80 для ФЛАНЦА</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Прокладка паронитовая для МС-140</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Ревизия 110мм</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>резина к таперу 50/75</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Резьба 15 стальная</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Резьба 20 стальная</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Резьба 40 стальная</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Резьба Ду-25</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Резьба Ду-32</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Резьба Ду-50</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Сгон 15 сталь</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Сгон 20 сталь</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Сгон 25 сталь</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Сгон 32 сталь</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Сгон 40 сталь</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Смазка силиконовая 250 гр РТП</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>штука 119 Тройник переходной 32*20*32</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Тройник переходной 32*32*32</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Тройник переходной 40х32х40</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>40×32</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Тройник 110*110/87 ( в уп.30шт)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Тройник 110х45х110</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>110×45</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Тройник 110*50/87</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Тройник 40х40х40</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>40×40</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Тройник 50*50/45</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Тройник 50*50/87</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Тройник 63*20*63</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Тройник 63х40х63</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>63×40</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Тройник 63х63х63</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>63×63</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Тройник переходной 25*20*25 ТЕВО(25/275)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Тройник переходной 32х25х32</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>32×25</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Тройник переходной 40х20х40</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>40×20</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Тройник полипропилен. 25</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Труба D 20 PN20 ПП</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Труба D 20 PN20 ПП стекловолокно</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Труба D 25 PN20 ПП</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Труба D 25 PN20 ПП стекловолокно</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Труба D 32 PN20 ПП</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Труба D 32 SDR 7.4 стекловолокно</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>32×4.3</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Труба D 40 PN20 ПП</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Труба D 40 SDR 6.0 СТЕКЛОВОЛОКНО</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>40×6.7</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Труба D 63 PN20 ПП</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ПП стекловолокно</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Труба канализационная ПП 110х1000</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>110×1000</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Труба канализационная ПП 110х1500</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>110×1500</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Труба канализационная ПП 110х2000</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>110×2000</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>штука 151 Угольник 20 45 град. ТЕВО</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Угольник 20 90 град. ТЕВО (50/550)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>штука 154 Угольник 32 90 град. ТЕВО</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Угольник 40 45 град. ТЕВО (10/120)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Угольник 40 90 град. ТЕВО (10/110)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Угольник d25 90 гр</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Угольник d32 45 гр</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Фланец ДУ 50</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Фланец ДУ 80</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Хомут ремонтный оцинк. Ду 32 1.1/4</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Хомут ремонтный оцинк. Ду 40 1.1/2</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Хомут ремонтный оцинк. Ду 50 (57-67)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>20×1</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Хомут ремонтный оцинк. Ду 80 3</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Валик универсальный 100мм</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Ванночка малярная 350*330мм</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Саморез ПШ острый 4.2 х 13</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Саморез ПШ острый 4.2 х 25</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Прессшайба 4*25</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="F158" s="5" t="n">
+        <v>0.155</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="G159" s="6" t="n">
         <v>1552247</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Источник: preview.txt</t>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Источник: preview_10.txt</t>
         </is>
       </c>
     </row>
